--- a/results/main/Figure_2_data_meta_1_heterogeneity_0_multilevel_random.xlsx
+++ b/results/main/Figure_2_data_meta_1_heterogeneity_0_multilevel_random.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
   <si>
     <t xml:space="preserve">cID</t>
   </si>
@@ -1818,6 +1818,9 @@
   </si>
   <si>
     <t xml:space="preserve">439-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439-3</t>
   </si>
   <si>
     <t xml:space="preserve">439-4</t>
@@ -25672,13 +25675,13 @@
         <v>439</v>
       </c>
       <c r="C564" t="n">
-        <v>0.945984499224202</v>
+        <v>0.234359278662947</v>
       </c>
       <c r="D564" t="n">
-        <v>0.571428571428571</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E564" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F564" t="s">
         <v>104</v>
@@ -25696,13 +25699,13 @@
         <v>22</v>
       </c>
       <c r="K564" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L564" t="n">
-        <v>94.6</v>
+        <v>23.44</v>
       </c>
       <c r="M564" t="n">
-        <v>57.14</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="565">
@@ -25710,19 +25713,19 @@
         <v>603</v>
       </c>
       <c r="B565" t="n">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="C565" t="n">
-        <v>0.340881511630782</v>
+        <v>0.945984499224202</v>
       </c>
       <c r="D565" t="n">
-        <v>0.181818181818182</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="E565" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F565" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G565" t="s">
         <v>20</v>
@@ -25737,13 +25740,13 @@
         <v>22</v>
       </c>
       <c r="K565" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L565" t="n">
-        <v>34.09</v>
+        <v>94.6</v>
       </c>
       <c r="M565" t="n">
-        <v>18.18</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="566">
@@ -25754,13 +25757,13 @@
         <v>460</v>
       </c>
       <c r="C566" t="n">
-        <v>0.176753471085384</v>
+        <v>0.340881511630782</v>
       </c>
       <c r="D566" t="n">
-        <v>0.333333333333333</v>
+        <v>0.181818181818182</v>
       </c>
       <c r="E566" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F566" t="s">
         <v>127</v>
@@ -25781,10 +25784,10 @@
         <v>15</v>
       </c>
       <c r="L566" t="n">
-        <v>17.68</v>
+        <v>34.09</v>
       </c>
       <c r="M566" t="n">
-        <v>33.33</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="567">
@@ -25795,13 +25798,13 @@
         <v>460</v>
       </c>
       <c r="C567" t="n">
-        <v>0.051777733418237</v>
+        <v>0.176753471085384</v>
       </c>
       <c r="D567" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E567" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F567" t="s">
         <v>127</v>
@@ -25822,10 +25825,10 @@
         <v>15</v>
       </c>
       <c r="L567" t="n">
-        <v>5.18</v>
+        <v>17.68</v>
       </c>
       <c r="M567" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="568">
@@ -25836,16 +25839,16 @@
         <v>460</v>
       </c>
       <c r="C568" t="n">
-        <v>0.761389807307596</v>
+        <v>0.051777733418237</v>
       </c>
       <c r="D568" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E568" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F568" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="G568" t="s">
         <v>20</v>
@@ -25863,10 +25866,10 @@
         <v>15</v>
       </c>
       <c r="L568" t="n">
-        <v>76.14</v>
+        <v>5.18</v>
       </c>
       <c r="M568" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -25877,13 +25880,13 @@
         <v>460</v>
       </c>
       <c r="C569" t="n">
-        <v>0.681728368704726</v>
+        <v>0.761389807307596</v>
       </c>
       <c r="D569" t="n">
         <v>0.5</v>
       </c>
       <c r="E569" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F569" t="s">
         <v>104</v>
@@ -25904,7 +25907,7 @@
         <v>15</v>
       </c>
       <c r="L569" t="n">
-        <v>68.17</v>
+        <v>76.14</v>
       </c>
       <c r="M569" t="n">
         <v>50</v>
@@ -25918,13 +25921,13 @@
         <v>460</v>
       </c>
       <c r="C570" t="n">
-        <v>0.98789909985894</v>
+        <v>0.681728368704726</v>
       </c>
       <c r="D570" t="n">
-        <v>0.545454545454545</v>
+        <v>0.5</v>
       </c>
       <c r="E570" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F570" t="s">
         <v>104</v>
@@ -25942,13 +25945,13 @@
         <v>22</v>
       </c>
       <c r="K570" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L570" t="n">
-        <v>98.79</v>
+        <v>68.17</v>
       </c>
       <c r="M570" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="571">
@@ -25956,19 +25959,19 @@
         <v>609</v>
       </c>
       <c r="B571" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C571" t="n">
-        <v>0.956248927346525</v>
+        <v>0.98789909985894</v>
       </c>
       <c r="D571" t="n">
-        <v>0.583333333333333</v>
+        <v>0.545454545454545</v>
       </c>
       <c r="E571" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F571" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G571" t="s">
         <v>20</v>
@@ -25977,19 +25980,19 @@
         <v>15</v>
       </c>
       <c r="I571" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J571" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K571" t="s">
         <v>20</v>
       </c>
       <c r="L571" t="n">
-        <v>95.62</v>
+        <v>98.79</v>
       </c>
       <c r="M571" t="n">
-        <v>58.33</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="572">
@@ -25997,19 +26000,19 @@
         <v>610</v>
       </c>
       <c r="B572" t="n">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="C572" t="n">
-        <v>0.787008746951921</v>
+        <v>0.956248927346525</v>
       </c>
       <c r="D572" t="n">
-        <v>0.5</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="E572" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G572" t="s">
         <v>20</v>
@@ -26018,19 +26021,19 @@
         <v>15</v>
       </c>
       <c r="I572" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J572" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K572" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L572" t="n">
-        <v>78.7</v>
+        <v>95.62</v>
       </c>
       <c r="M572" t="n">
-        <v>50</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="573">
@@ -26038,19 +26041,19 @@
         <v>611</v>
       </c>
       <c r="B573" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C573" t="n">
-        <v>0.066417653402202</v>
+        <v>0.787008746951921</v>
       </c>
       <c r="D573" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E573" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F573" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G573" t="s">
         <v>20</v>
@@ -26068,10 +26071,10 @@
         <v>15</v>
       </c>
       <c r="L573" t="n">
-        <v>6.64</v>
+        <v>78.7</v>
       </c>
       <c r="M573" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="574">
@@ -26082,10 +26085,10 @@
         <v>496</v>
       </c>
       <c r="C574" t="n">
-        <v>0.198471630847549</v>
+        <v>0.066417653402202</v>
       </c>
       <c r="D574" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E574" t="n">
         <v>5</v>
@@ -26109,10 +26112,10 @@
         <v>15</v>
       </c>
       <c r="L574" t="n">
-        <v>19.85</v>
+        <v>6.64</v>
       </c>
       <c r="M574" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="575">
@@ -26120,19 +26123,19 @@
         <v>613</v>
       </c>
       <c r="B575" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C575" t="n">
-        <v>0.2377699053124</v>
+        <v>0.198471630847549</v>
       </c>
       <c r="D575" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E575" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F575" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G575" t="s">
         <v>20</v>
@@ -26150,10 +26153,10 @@
         <v>15</v>
       </c>
       <c r="L575" t="n">
-        <v>23.78</v>
+        <v>19.85</v>
       </c>
       <c r="M575" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="576">
@@ -26164,10 +26167,10 @@
         <v>500</v>
       </c>
       <c r="C576" t="n">
-        <v>0.502924095321915</v>
+        <v>0.2377699053124</v>
       </c>
       <c r="D576" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E576" t="n">
         <v>6</v>
@@ -26191,10 +26194,10 @@
         <v>15</v>
       </c>
       <c r="L576" t="n">
-        <v>50.29</v>
+        <v>23.78</v>
       </c>
       <c r="M576" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
@@ -26205,13 +26208,13 @@
         <v>500</v>
       </c>
       <c r="C577" t="n">
-        <v>0.12594497070854</v>
+        <v>0.502924095321915</v>
       </c>
       <c r="D577" t="n">
-        <v>0.142857142857143</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E577" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F577" t="s">
         <v>104</v>
@@ -26232,10 +26235,10 @@
         <v>15</v>
       </c>
       <c r="L577" t="n">
-        <v>12.59</v>
+        <v>50.29</v>
       </c>
       <c r="M577" t="n">
-        <v>14.29</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="578">
@@ -26246,7 +26249,7 @@
         <v>500</v>
       </c>
       <c r="C578" t="n">
-        <v>0.271644893870655</v>
+        <v>0.12594497070854</v>
       </c>
       <c r="D578" t="n">
         <v>0.142857142857143</v>
@@ -26273,7 +26276,7 @@
         <v>15</v>
       </c>
       <c r="L578" t="n">
-        <v>27.16</v>
+        <v>12.59</v>
       </c>
       <c r="M578" t="n">
         <v>14.29</v>
@@ -26287,13 +26290,13 @@
         <v>500</v>
       </c>
       <c r="C579" t="n">
-        <v>0.404486053873488</v>
+        <v>0.271644893870655</v>
       </c>
       <c r="D579" t="n">
-        <v>0.2</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E579" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F579" t="s">
         <v>104</v>
@@ -26314,10 +26317,10 @@
         <v>15</v>
       </c>
       <c r="L579" t="n">
-        <v>40.45</v>
+        <v>27.16</v>
       </c>
       <c r="M579" t="n">
-        <v>20</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="580">
@@ -26325,28 +26328,28 @@
         <v>618</v>
       </c>
       <c r="B580" t="n">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="C580" t="n">
-        <v>0.0593986701216311</v>
+        <v>0.404486053873488</v>
       </c>
       <c r="D580" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E580" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F580" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G580" t="s">
         <v>20</v>
       </c>
       <c r="H580" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I580" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J580" t="s">
         <v>22</v>
@@ -26355,10 +26358,10 @@
         <v>15</v>
       </c>
       <c r="L580" t="n">
-        <v>5.94</v>
+        <v>40.45</v>
       </c>
       <c r="M580" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="581">
@@ -26369,13 +26372,13 @@
         <v>533</v>
       </c>
       <c r="C581" t="n">
-        <v>0.137279721216253</v>
+        <v>0.0593986701216311</v>
       </c>
       <c r="D581" t="n">
         <v>0</v>
       </c>
       <c r="E581" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F581" t="s">
         <v>14</v>
@@ -26396,7 +26399,7 @@
         <v>15</v>
       </c>
       <c r="L581" t="n">
-        <v>13.73</v>
+        <v>5.94</v>
       </c>
       <c r="M581" t="n">
         <v>0</v>
@@ -26410,13 +26413,13 @@
         <v>533</v>
       </c>
       <c r="C582" t="n">
-        <v>0.290690608648653</v>
+        <v>0.137279721216253</v>
       </c>
       <c r="D582" t="n">
         <v>0</v>
       </c>
       <c r="E582" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F582" t="s">
         <v>14</v>
@@ -26437,7 +26440,7 @@
         <v>15</v>
       </c>
       <c r="L582" t="n">
-        <v>29.07</v>
+        <v>13.73</v>
       </c>
       <c r="M582" t="n">
         <v>0</v>
@@ -26451,13 +26454,13 @@
         <v>533</v>
       </c>
       <c r="C583" t="n">
-        <v>0.0551133318862747</v>
+        <v>0.290690608648653</v>
       </c>
       <c r="D583" t="n">
         <v>0</v>
       </c>
       <c r="E583" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F583" t="s">
         <v>14</v>
@@ -26478,7 +26481,7 @@
         <v>15</v>
       </c>
       <c r="L583" t="n">
-        <v>5.51</v>
+        <v>29.07</v>
       </c>
       <c r="M583" t="n">
         <v>0</v>
@@ -26492,13 +26495,13 @@
         <v>533</v>
       </c>
       <c r="C584" t="n">
-        <v>0.0502614878233221</v>
+        <v>0.0551133318862747</v>
       </c>
       <c r="D584" t="n">
         <v>0</v>
       </c>
       <c r="E584" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F584" t="s">
         <v>14</v>
@@ -26519,7 +26522,7 @@
         <v>15</v>
       </c>
       <c r="L584" t="n">
-        <v>5.03</v>
+        <v>5.51</v>
       </c>
       <c r="M584" t="n">
         <v>0</v>
@@ -26533,13 +26536,13 @@
         <v>533</v>
       </c>
       <c r="C585" t="n">
-        <v>0.362765375815612</v>
+        <v>0.0502614878233221</v>
       </c>
       <c r="D585" t="n">
-        <v>0.0303030303030303</v>
+        <v>0</v>
       </c>
       <c r="E585" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F585" t="s">
         <v>14</v>
@@ -26560,10 +26563,10 @@
         <v>15</v>
       </c>
       <c r="L585" t="n">
-        <v>36.28</v>
+        <v>5.03</v>
       </c>
       <c r="M585" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="586">
@@ -26574,13 +26577,13 @@
         <v>533</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0646830308224397</v>
+        <v>0.362765375815612</v>
       </c>
       <c r="D586" t="n">
-        <v>0</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="E586" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F586" t="s">
         <v>14</v>
@@ -26601,10 +26604,10 @@
         <v>15</v>
       </c>
       <c r="L586" t="n">
-        <v>6.47</v>
+        <v>36.28</v>
       </c>
       <c r="M586" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="587">
@@ -26615,13 +26618,13 @@
         <v>533</v>
       </c>
       <c r="C587" t="n">
-        <v>0.0866073579688906</v>
+        <v>0.0646830308224397</v>
       </c>
       <c r="D587" t="n">
-        <v>0.0137931034482759</v>
+        <v>0</v>
       </c>
       <c r="E587" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F587" t="s">
         <v>14</v>
@@ -26642,10 +26645,10 @@
         <v>15</v>
       </c>
       <c r="L587" t="n">
-        <v>8.66</v>
+        <v>6.47</v>
       </c>
       <c r="M587" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -26653,40 +26656,40 @@
         <v>626</v>
       </c>
       <c r="B588" t="n">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C588" t="n">
-        <v>0.220675697723214</v>
+        <v>0.0866073579688906</v>
       </c>
       <c r="D588" t="n">
-        <v>0.107250755287009</v>
+        <v>0.0137931034482759</v>
       </c>
       <c r="E588" t="n">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="F588" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I588" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J588" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K588" t="s">
         <v>15</v>
       </c>
       <c r="L588" t="n">
-        <v>22.07</v>
+        <v>8.66</v>
       </c>
       <c r="M588" t="n">
-        <v>10.73</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="589">
@@ -26694,16 +26697,16 @@
         <v>627</v>
       </c>
       <c r="B589" t="n">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C589" t="n">
-        <v>0.438148781691134</v>
+        <v>0.220675697723214</v>
       </c>
       <c r="D589" t="n">
-        <v>0.108641975308642</v>
+        <v>0.107250755287009</v>
       </c>
       <c r="E589" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="F589" t="s">
         <v>26</v>
@@ -26715,7 +26718,7 @@
         <v>15</v>
       </c>
       <c r="I589" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J589" t="s">
         <v>17</v>
@@ -26724,10 +26727,10 @@
         <v>15</v>
       </c>
       <c r="L589" t="n">
-        <v>43.81</v>
+        <v>22.07</v>
       </c>
       <c r="M589" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="590">
@@ -26738,13 +26741,13 @@
         <v>547</v>
       </c>
       <c r="C590" t="n">
-        <v>0.10024244722945</v>
+        <v>0.438148781691134</v>
       </c>
       <c r="D590" t="n">
-        <v>0.00645161290322581</v>
+        <v>0.108641975308642</v>
       </c>
       <c r="E590" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F590" t="s">
         <v>26</v>
@@ -26765,10 +26768,10 @@
         <v>15</v>
       </c>
       <c r="L590" t="n">
-        <v>10.02</v>
+        <v>43.81</v>
       </c>
       <c r="M590" t="n">
-        <v>0.65</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="591">
@@ -26779,13 +26782,13 @@
         <v>547</v>
       </c>
       <c r="C591" t="n">
-        <v>0.841151852034752</v>
+        <v>0.10024244722945</v>
       </c>
       <c r="D591" t="n">
-        <v>0.727272727272727</v>
+        <v>0.00645161290322581</v>
       </c>
       <c r="E591" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F591" t="s">
         <v>26</v>
@@ -26803,13 +26806,13 @@
         <v>17</v>
       </c>
       <c r="K591" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L591" t="n">
-        <v>84.12</v>
+        <v>10.02</v>
       </c>
       <c r="M591" t="n">
-        <v>72.73</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="592">
@@ -26820,13 +26823,13 @@
         <v>547</v>
       </c>
       <c r="C592" t="n">
-        <v>0.0547113169515418</v>
+        <v>0.841151852034752</v>
       </c>
       <c r="D592" t="n">
-        <v>0</v>
+        <v>0.727272727272727</v>
       </c>
       <c r="E592" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F592" t="s">
         <v>26</v>
@@ -26844,13 +26847,13 @@
         <v>17</v>
       </c>
       <c r="K592" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L592" t="n">
-        <v>5.47</v>
+        <v>84.12</v>
       </c>
       <c r="M592" t="n">
-        <v>0</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="593">
@@ -26861,13 +26864,13 @@
         <v>547</v>
       </c>
       <c r="C593" t="n">
-        <v>0.0512759503682689</v>
+        <v>0.0547113169515418</v>
       </c>
       <c r="D593" t="n">
         <v>0</v>
       </c>
       <c r="E593" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F593" t="s">
         <v>26</v>
@@ -26888,7 +26891,7 @@
         <v>15</v>
       </c>
       <c r="L593" t="n">
-        <v>5.13</v>
+        <v>5.47</v>
       </c>
       <c r="M593" t="n">
         <v>0</v>
@@ -26902,13 +26905,13 @@
         <v>547</v>
       </c>
       <c r="C594" t="n">
-        <v>0.0519949117093046</v>
+        <v>0.0512759503682689</v>
       </c>
       <c r="D594" t="n">
         <v>0</v>
       </c>
       <c r="E594" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F594" t="s">
         <v>26</v>
@@ -26929,7 +26932,7 @@
         <v>15</v>
       </c>
       <c r="L594" t="n">
-        <v>5.2</v>
+        <v>5.13</v>
       </c>
       <c r="M594" t="n">
         <v>0</v>
@@ -26943,13 +26946,13 @@
         <v>547</v>
       </c>
       <c r="C595" t="n">
-        <v>0.250278755926891</v>
+        <v>0.0519949117093046</v>
       </c>
       <c r="D595" t="n">
-        <v>0.0605612998522895</v>
+        <v>0</v>
       </c>
       <c r="E595" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F595" t="s">
         <v>26</v>
@@ -26970,10 +26973,10 @@
         <v>15</v>
       </c>
       <c r="L595" t="n">
-        <v>25.03</v>
+        <v>5.2</v>
       </c>
       <c r="M595" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -26984,13 +26987,13 @@
         <v>547</v>
       </c>
       <c r="C596" t="n">
-        <v>0.602307054340794</v>
+        <v>0.250278755926891</v>
       </c>
       <c r="D596" t="n">
-        <v>0.27807486631016</v>
+        <v>0.0605612998522895</v>
       </c>
       <c r="E596" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F596" t="s">
         <v>26</v>
@@ -27011,10 +27014,10 @@
         <v>15</v>
       </c>
       <c r="L596" t="n">
-        <v>60.23</v>
+        <v>25.03</v>
       </c>
       <c r="M596" t="n">
-        <v>27.81</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="597">
@@ -27022,16 +27025,16 @@
         <v>635</v>
       </c>
       <c r="B597" t="n">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C597" t="n">
-        <v>0.491232640533953</v>
+        <v>0.602307054340794</v>
       </c>
       <c r="D597" t="n">
-        <v>0.354838709677419</v>
+        <v>0.27807486631016</v>
       </c>
       <c r="E597" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F597" t="s">
         <v>26</v>
@@ -27043,7 +27046,7 @@
         <v>15</v>
       </c>
       <c r="I597" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J597" t="s">
         <v>17</v>
@@ -27052,10 +27055,10 @@
         <v>15</v>
       </c>
       <c r="L597" t="n">
-        <v>49.12</v>
+        <v>60.23</v>
       </c>
       <c r="M597" t="n">
-        <v>35.48</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="598">
@@ -27066,13 +27069,13 @@
         <v>566</v>
       </c>
       <c r="C598" t="n">
-        <v>0.055877491832411</v>
+        <v>0.491232640533953</v>
       </c>
       <c r="D598" t="n">
-        <v>0.00869565217391304</v>
+        <v>0.354838709677419</v>
       </c>
       <c r="E598" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F598" t="s">
         <v>26</v>
@@ -27093,10 +27096,10 @@
         <v>15</v>
       </c>
       <c r="L598" t="n">
-        <v>5.59</v>
+        <v>49.12</v>
       </c>
       <c r="M598" t="n">
-        <v>0.87</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="599">
@@ -27107,13 +27110,13 @@
         <v>566</v>
       </c>
       <c r="C599" t="n">
-        <v>0.598424860376401</v>
+        <v>0.055877491832411</v>
       </c>
       <c r="D599" t="n">
-        <v>0.412371134020619</v>
+        <v>0.00869565217391304</v>
       </c>
       <c r="E599" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F599" t="s">
         <v>26</v>
@@ -27134,10 +27137,10 @@
         <v>15</v>
       </c>
       <c r="L599" t="n">
-        <v>59.84</v>
+        <v>5.59</v>
       </c>
       <c r="M599" t="n">
-        <v>41.24</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="600">
@@ -27148,13 +27151,13 @@
         <v>566</v>
       </c>
       <c r="C600" t="n">
-        <v>1</v>
+        <v>0.598424860376401</v>
       </c>
       <c r="D600" t="n">
-        <v>0.947761194029851</v>
+        <v>0.412371134020619</v>
       </c>
       <c r="E600" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F600" t="s">
         <v>26</v>
@@ -27172,13 +27175,13 @@
         <v>17</v>
       </c>
       <c r="K600" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L600" t="n">
-        <v>100</v>
+        <v>59.84</v>
       </c>
       <c r="M600" t="n">
-        <v>94.78</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="601">
@@ -27189,13 +27192,13 @@
         <v>566</v>
       </c>
       <c r="C601" t="n">
-        <v>0.472708925264846</v>
+        <v>1</v>
       </c>
       <c r="D601" t="n">
-        <v>0.37410071942446</v>
+        <v>0.947761194029851</v>
       </c>
       <c r="E601" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F601" t="s">
         <v>26</v>
@@ -27213,13 +27216,13 @@
         <v>17</v>
       </c>
       <c r="K601" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L601" t="n">
-        <v>47.27</v>
+        <v>100</v>
       </c>
       <c r="M601" t="n">
-        <v>37.41</v>
+        <v>94.78</v>
       </c>
     </row>
     <row r="602">
@@ -27230,13 +27233,13 @@
         <v>566</v>
       </c>
       <c r="C602" t="n">
-        <v>0.133378083442036</v>
+        <v>0.472708925264846</v>
       </c>
       <c r="D602" t="n">
-        <v>0.0897435897435897</v>
+        <v>0.37410071942446</v>
       </c>
       <c r="E602" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F602" t="s">
         <v>26</v>
@@ -27257,10 +27260,10 @@
         <v>15</v>
       </c>
       <c r="L602" t="n">
-        <v>13.34</v>
+        <v>47.27</v>
       </c>
       <c r="M602" t="n">
-        <v>8.97</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="603">
@@ -27271,13 +27274,13 @@
         <v>566</v>
       </c>
       <c r="C603" t="n">
-        <v>0.101041422939802</v>
+        <v>0.133378083442036</v>
       </c>
       <c r="D603" t="n">
-        <v>0</v>
+        <v>0.0897435897435897</v>
       </c>
       <c r="E603" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F603" t="s">
         <v>26</v>
@@ -27298,10 +27301,10 @@
         <v>15</v>
       </c>
       <c r="L603" t="n">
-        <v>10.1</v>
+        <v>13.34</v>
       </c>
       <c r="M603" t="n">
-        <v>0</v>
+        <v>8.97</v>
       </c>
     </row>
     <row r="604">
@@ -27312,13 +27315,13 @@
         <v>566</v>
       </c>
       <c r="C604" t="n">
-        <v>0.253192693528731</v>
+        <v>0.101041422939802</v>
       </c>
       <c r="D604" t="n">
-        <v>0.188524590163934</v>
+        <v>0</v>
       </c>
       <c r="E604" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F604" t="s">
         <v>26</v>
@@ -27339,10 +27342,10 @@
         <v>15</v>
       </c>
       <c r="L604" t="n">
-        <v>25.32</v>
+        <v>10.1</v>
       </c>
       <c r="M604" t="n">
-        <v>18.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="605">
@@ -27353,13 +27356,13 @@
         <v>566</v>
       </c>
       <c r="C605" t="n">
-        <v>0.343127376089836</v>
+        <v>0.253192693528731</v>
       </c>
       <c r="D605" t="n">
-        <v>0.25</v>
+        <v>0.188524590163934</v>
       </c>
       <c r="E605" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F605" t="s">
         <v>26</v>
@@ -27380,10 +27383,10 @@
         <v>15</v>
       </c>
       <c r="L605" t="n">
-        <v>34.31</v>
+        <v>25.32</v>
       </c>
       <c r="M605" t="n">
-        <v>25</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="606">
@@ -27394,13 +27397,13 @@
         <v>566</v>
       </c>
       <c r="C606" t="n">
-        <v>0.43395414188976</v>
+        <v>0.343127376089836</v>
       </c>
       <c r="D606" t="n">
-        <v>0.337837837837838</v>
+        <v>0.25</v>
       </c>
       <c r="E606" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>26</v>
@@ -27421,10 +27424,10 @@
         <v>15</v>
       </c>
       <c r="L606" t="n">
-        <v>43.4</v>
+        <v>34.31</v>
       </c>
       <c r="M606" t="n">
-        <v>33.78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="607">
@@ -27435,13 +27438,13 @@
         <v>566</v>
       </c>
       <c r="C607" t="n">
-        <v>0.189258290906981</v>
+        <v>0.43395414188976</v>
       </c>
       <c r="D607" t="n">
-        <v>0.165137614678899</v>
+        <v>0.337837837837838</v>
       </c>
       <c r="E607" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F607" t="s">
         <v>26</v>
@@ -27462,10 +27465,10 @@
         <v>15</v>
       </c>
       <c r="L607" t="n">
-        <v>18.93</v>
+        <v>43.4</v>
       </c>
       <c r="M607" t="n">
-        <v>16.51</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="608">
@@ -27473,40 +27476,40 @@
         <v>646</v>
       </c>
       <c r="B608" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="C608" t="n">
-        <v>0.901889951637554</v>
+        <v>0.189258290906981</v>
       </c>
       <c r="D608" t="n">
-        <v>0.561224489795918</v>
+        <v>0.165137614678899</v>
       </c>
       <c r="E608" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F608" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I608" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J608" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L608" t="n">
-        <v>90.19</v>
+        <v>18.93</v>
       </c>
       <c r="M608" t="n">
-        <v>56.12</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="609">
@@ -27517,13 +27520,13 @@
         <v>581</v>
       </c>
       <c r="C609" t="n">
-        <v>0.22966402280817</v>
+        <v>0.901889951637554</v>
       </c>
       <c r="D609" t="n">
-        <v>0.101694915254237</v>
+        <v>0.561224489795918</v>
       </c>
       <c r="E609" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>24</v>
@@ -27541,13 +27544,13 @@
         <v>22</v>
       </c>
       <c r="K609" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L609" t="n">
-        <v>22.97</v>
+        <v>90.19</v>
       </c>
       <c r="M609" t="n">
-        <v>10.17</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="610">
@@ -27555,40 +27558,40 @@
         <v>648</v>
       </c>
       <c r="B610" t="n">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C610" t="n">
-        <v>0.969948414134332</v>
+        <v>0.22966402280817</v>
       </c>
       <c r="D610" t="n">
-        <v>0.714285714285714</v>
+        <v>0.101694915254237</v>
       </c>
       <c r="E610" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I610" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J610" t="s">
         <v>22</v>
       </c>
       <c r="K610" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L610" t="n">
-        <v>96.99</v>
+        <v>22.97</v>
       </c>
       <c r="M610" t="n">
-        <v>71.43</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="611">
@@ -27599,13 +27602,13 @@
         <v>608</v>
       </c>
       <c r="C611" t="n">
-        <v>0.997083325908069</v>
+        <v>0.969948414134332</v>
       </c>
       <c r="D611" t="n">
-        <v>0.882352941176471</v>
+        <v>0.714285714285714</v>
       </c>
       <c r="E611" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>19</v>
@@ -27626,10 +27629,10 @@
         <v>20</v>
       </c>
       <c r="L611" t="n">
-        <v>99.71</v>
+        <v>96.99</v>
       </c>
       <c r="M611" t="n">
-        <v>88.24</v>
+        <v>71.43</v>
       </c>
     </row>
     <row r="612">
@@ -27640,13 +27643,13 @@
         <v>608</v>
       </c>
       <c r="C612" t="n">
-        <v>1</v>
+        <v>0.997083325908069</v>
       </c>
       <c r="D612" t="n">
-        <v>1</v>
+        <v>0.882352941176471</v>
       </c>
       <c r="E612" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F612" t="s">
         <v>19</v>
@@ -27667,10 +27670,10 @@
         <v>20</v>
       </c>
       <c r="L612" t="n">
-        <v>100</v>
+        <v>99.71</v>
       </c>
       <c r="M612" t="n">
-        <v>100</v>
+        <v>88.24</v>
       </c>
     </row>
     <row r="613">
@@ -27678,19 +27681,19 @@
         <v>651</v>
       </c>
       <c r="B613" t="n">
-        <v>62</v>
+        <v>608</v>
       </c>
       <c r="C613" t="n">
-        <v>0.365424391815281</v>
+        <v>1</v>
       </c>
       <c r="D613" t="n">
-        <v>0.222222222222222</v>
+        <v>1</v>
       </c>
       <c r="E613" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G613" t="s">
         <v>15</v>
@@ -27699,19 +27702,19 @@
         <v>15</v>
       </c>
       <c r="I613" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J613" t="s">
         <v>22</v>
       </c>
       <c r="K613" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L613" t="n">
-        <v>36.54</v>
+        <v>100</v>
       </c>
       <c r="M613" t="n">
-        <v>22.22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="614">
@@ -27722,13 +27725,13 @@
         <v>62</v>
       </c>
       <c r="C614" t="n">
-        <v>0.0732519347618983</v>
+        <v>0.365424391815281</v>
       </c>
       <c r="D614" t="n">
-        <v>0</v>
+        <v>0.222222222222222</v>
       </c>
       <c r="E614" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F614" t="s">
         <v>14</v>
@@ -27749,10 +27752,10 @@
         <v>15</v>
       </c>
       <c r="L614" t="n">
-        <v>7.33</v>
+        <v>36.54</v>
       </c>
       <c r="M614" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="615">
@@ -27760,19 +27763,19 @@
         <v>653</v>
       </c>
       <c r="B615" t="n">
-        <v>623</v>
+        <v>62</v>
       </c>
       <c r="C615" t="n">
-        <v>0.0835709637277445</v>
+        <v>0.0732519347618983</v>
       </c>
       <c r="D615" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E615" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F615" t="s">
-        <v>393</v>
+        <v>14</v>
       </c>
       <c r="G615" t="s">
         <v>15</v>
@@ -27781,7 +27784,7 @@
         <v>15</v>
       </c>
       <c r="I615" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J615" t="s">
         <v>22</v>
@@ -27790,10 +27793,10 @@
         <v>15</v>
       </c>
       <c r="L615" t="n">
-        <v>8.36</v>
+        <v>7.33</v>
       </c>
       <c r="M615" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
@@ -27804,13 +27807,13 @@
         <v>623</v>
       </c>
       <c r="C616" t="n">
-        <v>0.24285486669644</v>
+        <v>0.0835709637277445</v>
       </c>
       <c r="D616" t="n">
-        <v>0.166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="E616" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F616" t="s">
         <v>393</v>
@@ -27831,10 +27834,10 @@
         <v>15</v>
       </c>
       <c r="L616" t="n">
-        <v>24.29</v>
+        <v>8.36</v>
       </c>
       <c r="M616" t="n">
-        <v>16.67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="617">
@@ -27842,19 +27845,19 @@
         <v>655</v>
       </c>
       <c r="B617" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C617" t="n">
-        <v>0.355386924399002</v>
+        <v>0.24285486669644</v>
       </c>
       <c r="D617" t="n">
-        <v>0.322314049586777</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E617" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F617" t="s">
-        <v>26</v>
+        <v>393</v>
       </c>
       <c r="G617" t="s">
         <v>15</v>
@@ -27866,16 +27869,16 @@
         <v>34</v>
       </c>
       <c r="J617" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K617" t="s">
         <v>15</v>
       </c>
       <c r="L617" t="n">
-        <v>35.54</v>
+        <v>24.29</v>
       </c>
       <c r="M617" t="n">
-        <v>32.23</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="618">
@@ -27886,13 +27889,13 @@
         <v>624</v>
       </c>
       <c r="C618" t="n">
-        <v>0.0756988746593162</v>
+        <v>0.355386924399002</v>
       </c>
       <c r="D618" t="n">
-        <v>0.0261437908496732</v>
+        <v>0.322314049586777</v>
       </c>
       <c r="E618" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F618" t="s">
         <v>26</v>
@@ -27913,10 +27916,10 @@
         <v>15</v>
       </c>
       <c r="L618" t="n">
-        <v>7.57</v>
+        <v>35.54</v>
       </c>
       <c r="M618" t="n">
-        <v>2.61</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="619">
@@ -27927,13 +27930,13 @@
         <v>624</v>
       </c>
       <c r="C619" t="n">
-        <v>0.205810938916091</v>
+        <v>0.0756988746593162</v>
       </c>
       <c r="D619" t="n">
-        <v>0.162011173184358</v>
+        <v>0.0261437908496732</v>
       </c>
       <c r="E619" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F619" t="s">
         <v>26</v>
@@ -27954,10 +27957,10 @@
         <v>15</v>
       </c>
       <c r="L619" t="n">
-        <v>20.58</v>
+        <v>7.57</v>
       </c>
       <c r="M619" t="n">
-        <v>16.2</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="620">
@@ -27965,40 +27968,40 @@
         <v>658</v>
       </c>
       <c r="B620" t="n">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C620" t="n">
-        <v>0.210615598202953</v>
+        <v>0.205810938916091</v>
       </c>
       <c r="D620" t="n">
-        <v>0.111111111111111</v>
+        <v>0.162011173184358</v>
       </c>
       <c r="E620" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F620" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G620" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H620" t="s">
         <v>15</v>
       </c>
       <c r="I620" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J620" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K620" t="s">
         <v>15</v>
       </c>
       <c r="L620" t="n">
-        <v>21.06</v>
+        <v>20.58</v>
       </c>
       <c r="M620" t="n">
-        <v>11.11</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="621">
@@ -28009,13 +28012,13 @@
         <v>625</v>
       </c>
       <c r="C621" t="n">
-        <v>0.422567899776942</v>
+        <v>0.210615598202953</v>
       </c>
       <c r="D621" t="n">
-        <v>0.301369863013699</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="E621" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F621" t="s">
         <v>100</v>
@@ -28036,10 +28039,10 @@
         <v>15</v>
       </c>
       <c r="L621" t="n">
-        <v>42.26</v>
+        <v>21.06</v>
       </c>
       <c r="M621" t="n">
-        <v>30.14</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="622">
@@ -28050,13 +28053,13 @@
         <v>625</v>
       </c>
       <c r="C622" t="n">
-        <v>0.206465568695968</v>
+        <v>0.422567899776942</v>
       </c>
       <c r="D622" t="n">
-        <v>0</v>
+        <v>0.301369863013699</v>
       </c>
       <c r="E622" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F622" t="s">
         <v>100</v>
@@ -28077,10 +28080,10 @@
         <v>15</v>
       </c>
       <c r="L622" t="n">
-        <v>20.65</v>
+        <v>42.26</v>
       </c>
       <c r="M622" t="n">
-        <v>0</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="623">
@@ -28088,19 +28091,19 @@
         <v>661</v>
       </c>
       <c r="B623" t="n">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="C623" t="n">
-        <v>0.0891244621348019</v>
+        <v>0.206465568695968</v>
       </c>
       <c r="D623" t="n">
         <v>0</v>
       </c>
       <c r="E623" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G623" t="s">
         <v>20</v>
@@ -28118,7 +28121,7 @@
         <v>15</v>
       </c>
       <c r="L623" t="n">
-        <v>8.91</v>
+        <v>20.65</v>
       </c>
       <c r="M623" t="n">
         <v>0</v>
@@ -28132,13 +28135,13 @@
         <v>63</v>
       </c>
       <c r="C624" t="n">
-        <v>0.060926832089909</v>
+        <v>0.0891244621348019</v>
       </c>
       <c r="D624" t="n">
         <v>0</v>
       </c>
       <c r="E624" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F624" t="s">
         <v>104</v>
@@ -28159,7 +28162,7 @@
         <v>15</v>
       </c>
       <c r="L624" t="n">
-        <v>6.09</v>
+        <v>8.91</v>
       </c>
       <c r="M624" t="n">
         <v>0</v>
@@ -28173,7 +28176,7 @@
         <v>63</v>
       </c>
       <c r="C625" t="n">
-        <v>0.0801522273431712</v>
+        <v>0.060926832089909</v>
       </c>
       <c r="D625" t="n">
         <v>0</v>
@@ -28200,7 +28203,7 @@
         <v>15</v>
       </c>
       <c r="L625" t="n">
-        <v>8.02</v>
+        <v>6.09</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
@@ -28214,13 +28217,13 @@
         <v>63</v>
       </c>
       <c r="C626" t="n">
-        <v>0.114536185340336</v>
+        <v>0.0801522273431712</v>
       </c>
       <c r="D626" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E626" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F626" t="s">
         <v>104</v>
@@ -28241,10 +28244,10 @@
         <v>15</v>
       </c>
       <c r="L626" t="n">
-        <v>11.45</v>
+        <v>8.02</v>
       </c>
       <c r="M626" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
@@ -28255,13 +28258,13 @@
         <v>63</v>
       </c>
       <c r="C627" t="n">
-        <v>0.0500478513776021</v>
+        <v>0.114536185340336</v>
       </c>
       <c r="D627" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E627" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>104</v>
@@ -28282,10 +28285,10 @@
         <v>15</v>
       </c>
       <c r="L627" t="n">
-        <v>5</v>
+        <v>11.45</v>
       </c>
       <c r="M627" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="628">
@@ -28296,13 +28299,13 @@
         <v>63</v>
       </c>
       <c r="C628" t="n">
-        <v>0.0510097970953678</v>
+        <v>0.0500478513776021</v>
       </c>
       <c r="D628" t="n">
         <v>0</v>
       </c>
       <c r="E628" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F628" t="s">
         <v>104</v>
@@ -28323,7 +28326,7 @@
         <v>15</v>
       </c>
       <c r="L628" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M628" t="n">
         <v>0</v>
@@ -28337,13 +28340,13 @@
         <v>63</v>
       </c>
       <c r="C629" t="n">
-        <v>0.0518441855263202</v>
+        <v>0.0510097970953678</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
       </c>
       <c r="E629" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F629" t="s">
         <v>104</v>
@@ -28364,7 +28367,7 @@
         <v>15</v>
       </c>
       <c r="L629" t="n">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
       <c r="M629" t="n">
         <v>0</v>
@@ -28378,13 +28381,13 @@
         <v>63</v>
       </c>
       <c r="C630" t="n">
-        <v>0.0519302879791397</v>
+        <v>0.0518441855263202</v>
       </c>
       <c r="D630" t="n">
         <v>0</v>
       </c>
       <c r="E630" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>104</v>
@@ -28405,7 +28408,7 @@
         <v>15</v>
       </c>
       <c r="L630" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="M630" t="n">
         <v>0</v>
@@ -28419,13 +28422,13 @@
         <v>63</v>
       </c>
       <c r="C631" t="n">
-        <v>0.0557327719132905</v>
+        <v>0.0519302879791397</v>
       </c>
       <c r="D631" t="n">
         <v>0</v>
       </c>
       <c r="E631" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F631" t="s">
         <v>104</v>
@@ -28446,7 +28449,7 @@
         <v>15</v>
       </c>
       <c r="L631" t="n">
-        <v>5.57</v>
+        <v>5.19</v>
       </c>
       <c r="M631" t="n">
         <v>0</v>
@@ -28460,13 +28463,13 @@
         <v>63</v>
       </c>
       <c r="C632" t="n">
-        <v>0.0810267222708388</v>
+        <v>0.0557327719132905</v>
       </c>
       <c r="D632" t="n">
         <v>0</v>
       </c>
       <c r="E632" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F632" t="s">
         <v>104</v>
@@ -28487,7 +28490,7 @@
         <v>15</v>
       </c>
       <c r="L632" t="n">
-        <v>8.1</v>
+        <v>5.57</v>
       </c>
       <c r="M632" t="n">
         <v>0</v>
@@ -28501,13 +28504,13 @@
         <v>63</v>
       </c>
       <c r="C633" t="n">
-        <v>0.0695617308664768</v>
+        <v>0.0810267222708388</v>
       </c>
       <c r="D633" t="n">
         <v>0</v>
       </c>
       <c r="E633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>104</v>
@@ -28528,7 +28531,7 @@
         <v>15</v>
       </c>
       <c r="L633" t="n">
-        <v>6.96</v>
+        <v>8.1</v>
       </c>
       <c r="M633" t="n">
         <v>0</v>
@@ -28542,13 +28545,13 @@
         <v>63</v>
       </c>
       <c r="C634" t="n">
-        <v>0.0581549794888311</v>
+        <v>0.0695617308664768</v>
       </c>
       <c r="D634" t="n">
         <v>0</v>
       </c>
       <c r="E634" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>104</v>
@@ -28569,7 +28572,7 @@
         <v>15</v>
       </c>
       <c r="L634" t="n">
-        <v>5.82</v>
+        <v>6.96</v>
       </c>
       <c r="M634" t="n">
         <v>0</v>
@@ -28583,13 +28586,13 @@
         <v>63</v>
       </c>
       <c r="C635" t="n">
-        <v>0.0661420662807675</v>
+        <v>0.0581549794888311</v>
       </c>
       <c r="D635" t="n">
         <v>0</v>
       </c>
       <c r="E635" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F635" t="s">
         <v>104</v>
@@ -28610,7 +28613,7 @@
         <v>15</v>
       </c>
       <c r="L635" t="n">
-        <v>6.61</v>
+        <v>5.82</v>
       </c>
       <c r="M635" t="n">
         <v>0</v>
@@ -28624,13 +28627,13 @@
         <v>63</v>
       </c>
       <c r="C636" t="n">
-        <v>0.210045573281954</v>
+        <v>0.0661420662807675</v>
       </c>
       <c r="D636" t="n">
         <v>0</v>
       </c>
       <c r="E636" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>104</v>
@@ -28651,7 +28654,7 @@
         <v>15</v>
       </c>
       <c r="L636" t="n">
-        <v>21</v>
+        <v>6.61</v>
       </c>
       <c r="M636" t="n">
         <v>0</v>
@@ -28665,13 +28668,13 @@
         <v>63</v>
       </c>
       <c r="C637" t="n">
-        <v>0.132431831647382</v>
+        <v>0.210045573281954</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
       </c>
       <c r="E637" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>104</v>
@@ -28692,7 +28695,7 @@
         <v>15</v>
       </c>
       <c r="L637" t="n">
-        <v>13.24</v>
+        <v>21</v>
       </c>
       <c r="M637" t="n">
         <v>0</v>
@@ -28706,13 +28709,13 @@
         <v>63</v>
       </c>
       <c r="C638" t="n">
-        <v>0.0557211258706848</v>
+        <v>0.132431831647382</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
       </c>
       <c r="E638" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F638" t="s">
         <v>104</v>
@@ -28733,7 +28736,7 @@
         <v>15</v>
       </c>
       <c r="L638" t="n">
-        <v>5.57</v>
+        <v>13.24</v>
       </c>
       <c r="M638" t="n">
         <v>0</v>
@@ -28747,13 +28750,13 @@
         <v>63</v>
       </c>
       <c r="C639" t="n">
-        <v>0.0697303529458719</v>
+        <v>0.0557211258706848</v>
       </c>
       <c r="D639" t="n">
         <v>0</v>
       </c>
       <c r="E639" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>104</v>
@@ -28774,7 +28777,7 @@
         <v>15</v>
       </c>
       <c r="L639" t="n">
-        <v>6.97</v>
+        <v>5.57</v>
       </c>
       <c r="M639" t="n">
         <v>0</v>
@@ -28788,13 +28791,13 @@
         <v>63</v>
       </c>
       <c r="C640" t="n">
-        <v>0.120946632914704</v>
+        <v>0.0697303529458719</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
       </c>
       <c r="E640" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>104</v>
@@ -28815,7 +28818,7 @@
         <v>15</v>
       </c>
       <c r="L640" t="n">
-        <v>12.09</v>
+        <v>6.97</v>
       </c>
       <c r="M640" t="n">
         <v>0</v>
@@ -28829,13 +28832,13 @@
         <v>63</v>
       </c>
       <c r="C641" t="n">
-        <v>0.0533918923380193</v>
+        <v>0.120946632914704</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
       </c>
       <c r="E641" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F641" t="s">
         <v>104</v>
@@ -28856,7 +28859,7 @@
         <v>15</v>
       </c>
       <c r="L641" t="n">
-        <v>5.34</v>
+        <v>12.09</v>
       </c>
       <c r="M641" t="n">
         <v>0</v>
@@ -28870,13 +28873,13 @@
         <v>63</v>
       </c>
       <c r="C642" t="n">
-        <v>0.243071222323783</v>
+        <v>0.0533918923380193</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
       </c>
       <c r="E642" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F642" t="s">
         <v>104</v>
@@ -28897,7 +28900,7 @@
         <v>15</v>
       </c>
       <c r="L642" t="n">
-        <v>24.31</v>
+        <v>5.34</v>
       </c>
       <c r="M642" t="n">
         <v>0</v>
@@ -28911,7 +28914,7 @@
         <v>63</v>
       </c>
       <c r="C643" t="n">
-        <v>0.0897868728782174</v>
+        <v>0.243071222323783</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -28938,7 +28941,7 @@
         <v>15</v>
       </c>
       <c r="L643" t="n">
-        <v>8.98</v>
+        <v>24.31</v>
       </c>
       <c r="M643" t="n">
         <v>0</v>
@@ -28952,13 +28955,13 @@
         <v>63</v>
       </c>
       <c r="C644" t="n">
-        <v>0.107762103642189</v>
+        <v>0.0897868728782174</v>
       </c>
       <c r="D644" t="n">
         <v>0</v>
       </c>
       <c r="E644" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>104</v>
@@ -28979,7 +28982,7 @@
         <v>15</v>
       </c>
       <c r="L644" t="n">
-        <v>10.78</v>
+        <v>8.98</v>
       </c>
       <c r="M644" t="n">
         <v>0</v>
@@ -28993,13 +28996,13 @@
         <v>63</v>
       </c>
       <c r="C645" t="n">
-        <v>0.0687913566323183</v>
+        <v>0.107762103642189</v>
       </c>
       <c r="D645" t="n">
         <v>0</v>
       </c>
       <c r="E645" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F645" t="s">
         <v>104</v>
@@ -29020,7 +29023,7 @@
         <v>15</v>
       </c>
       <c r="L645" t="n">
-        <v>6.88</v>
+        <v>10.78</v>
       </c>
       <c r="M645" t="n">
         <v>0</v>
@@ -29031,40 +29034,40 @@
         <v>684</v>
       </c>
       <c r="B646" t="n">
-        <v>651</v>
+        <v>63</v>
       </c>
       <c r="C646" t="n">
-        <v>0.203721135691349</v>
+        <v>0.0687913566323183</v>
       </c>
       <c r="D646" t="n">
-        <v>0.140495867768595</v>
+        <v>0</v>
       </c>
       <c r="E646" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="F646" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G646" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H646" t="s">
         <v>15</v>
       </c>
       <c r="I646" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J646" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K646" t="s">
         <v>15</v>
       </c>
       <c r="L646" t="n">
-        <v>20.37</v>
+        <v>6.88</v>
       </c>
       <c r="M646" t="n">
-        <v>14.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647">
@@ -29072,40 +29075,40 @@
         <v>685</v>
       </c>
       <c r="B647" t="n">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="C647" t="n">
-        <v>0.21559426009684</v>
+        <v>0.203721135691349</v>
       </c>
       <c r="D647" t="n">
-        <v>0.153846153846154</v>
+        <v>0.140495867768595</v>
       </c>
       <c r="E647" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="F647" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="G647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I647" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J647" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K647" t="s">
         <v>15</v>
       </c>
       <c r="L647" t="n">
-        <v>21.56</v>
+        <v>20.37</v>
       </c>
       <c r="M647" t="n">
-        <v>15.38</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="648">
@@ -29116,13 +29119,13 @@
         <v>715</v>
       </c>
       <c r="C648" t="n">
-        <v>0.263814951324111</v>
+        <v>0.21559426009684</v>
       </c>
       <c r="D648" t="n">
-        <v>0.166666666666667</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="E648" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F648" t="s">
         <v>127</v>
@@ -29143,10 +29146,10 @@
         <v>15</v>
       </c>
       <c r="L648" t="n">
-        <v>26.38</v>
+        <v>21.56</v>
       </c>
       <c r="M648" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="649">
@@ -29157,10 +29160,10 @@
         <v>715</v>
       </c>
       <c r="C649" t="n">
-        <v>0.095227195081937</v>
+        <v>0.263814951324111</v>
       </c>
       <c r="D649" t="n">
-        <v>0.0625</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E649" t="n">
         <v>6</v>
@@ -29184,10 +29187,10 @@
         <v>15</v>
       </c>
       <c r="L649" t="n">
-        <v>9.52</v>
+        <v>26.38</v>
       </c>
       <c r="M649" t="n">
-        <v>6.25</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="650">
@@ -29195,40 +29198,40 @@
         <v>688</v>
       </c>
       <c r="B650" t="n">
-        <v>753</v>
+        <v>715</v>
       </c>
       <c r="C650" t="n">
-        <v>0.163037276862448</v>
+        <v>0.095227195081937</v>
       </c>
       <c r="D650" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="E650" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F650" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
       </c>
       <c r="H650" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I650" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J650" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K650" t="s">
         <v>15</v>
       </c>
       <c r="L650" t="n">
-        <v>16.3</v>
+        <v>9.52</v>
       </c>
       <c r="M650" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="651">
@@ -29239,7 +29242,7 @@
         <v>753</v>
       </c>
       <c r="C651" t="n">
-        <v>0.0512839904453613</v>
+        <v>0.163037276862448</v>
       </c>
       <c r="D651" t="n">
         <v>0</v>
@@ -29266,7 +29269,7 @@
         <v>15</v>
       </c>
       <c r="L651" t="n">
-        <v>5.13</v>
+        <v>16.3</v>
       </c>
       <c r="M651" t="n">
         <v>0</v>
@@ -29280,7 +29283,7 @@
         <v>753</v>
       </c>
       <c r="C652" t="n">
-        <v>0.0825674601500757</v>
+        <v>0.0512839904453613</v>
       </c>
       <c r="D652" t="n">
         <v>0</v>
@@ -29307,7 +29310,7 @@
         <v>15</v>
       </c>
       <c r="L652" t="n">
-        <v>8.26</v>
+        <v>5.13</v>
       </c>
       <c r="M652" t="n">
         <v>0</v>
@@ -29321,7 +29324,7 @@
         <v>753</v>
       </c>
       <c r="C653" t="n">
-        <v>0.0787284148205731</v>
+        <v>0.0825674601500757</v>
       </c>
       <c r="D653" t="n">
         <v>0</v>
@@ -29348,7 +29351,7 @@
         <v>15</v>
       </c>
       <c r="L653" t="n">
-        <v>7.87</v>
+        <v>8.26</v>
       </c>
       <c r="M653" t="n">
         <v>0</v>
@@ -29362,10 +29365,10 @@
         <v>753</v>
       </c>
       <c r="C654" t="n">
-        <v>0.684480644186857</v>
+        <v>0.0787284148205731</v>
       </c>
       <c r="D654" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E654" t="n">
         <v>5</v>
@@ -29389,10 +29392,10 @@
         <v>15</v>
       </c>
       <c r="L654" t="n">
-        <v>68.45</v>
+        <v>7.87</v>
       </c>
       <c r="M654" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="655">
@@ -29400,22 +29403,22 @@
         <v>693</v>
       </c>
       <c r="B655" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C655" t="n">
-        <v>0.539057936109086</v>
+        <v>0.684480644186857</v>
       </c>
       <c r="D655" t="n">
-        <v>0.387096774193548</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E655" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G655" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H655" t="s">
         <v>15</v>
@@ -29424,16 +29427,16 @@
         <v>46</v>
       </c>
       <c r="J655" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K655" t="s">
         <v>15</v>
       </c>
       <c r="L655" t="n">
-        <v>53.91</v>
+        <v>68.45</v>
       </c>
       <c r="M655" t="n">
-        <v>38.71</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="656">
@@ -29441,19 +29444,19 @@
         <v>694</v>
       </c>
       <c r="B656" t="n">
-        <v>813</v>
+        <v>755</v>
       </c>
       <c r="C656" t="n">
-        <v>0.0773002280587221</v>
+        <v>0.539057936109086</v>
       </c>
       <c r="D656" t="n">
-        <v>0.0169491525423729</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="E656" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F656" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G656" t="s">
         <v>15</v>
@@ -29462,19 +29465,19 @@
         <v>15</v>
       </c>
       <c r="I656" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J656" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K656" t="s">
         <v>15</v>
       </c>
       <c r="L656" t="n">
-        <v>7.73</v>
+        <v>53.91</v>
       </c>
       <c r="M656" t="n">
-        <v>1.69</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="657">
@@ -29485,13 +29488,13 @@
         <v>813</v>
       </c>
       <c r="C657" t="n">
-        <v>0.221309094315629</v>
+        <v>0.0773002280587221</v>
       </c>
       <c r="D657" t="n">
-        <v>0.125</v>
+        <v>0.0169491525423729</v>
       </c>
       <c r="E657" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F657" t="s">
         <v>104</v>
@@ -29512,10 +29515,10 @@
         <v>15</v>
       </c>
       <c r="L657" t="n">
-        <v>22.13</v>
+        <v>7.73</v>
       </c>
       <c r="M657" t="n">
-        <v>12.5</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="658">
@@ -29526,16 +29529,16 @@
         <v>813</v>
       </c>
       <c r="C658" t="n">
-        <v>0.107972772561798</v>
+        <v>0.221309094315629</v>
       </c>
       <c r="D658" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E658" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F658" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G658" t="s">
         <v>15</v>
@@ -29553,10 +29556,10 @@
         <v>15</v>
       </c>
       <c r="L658" t="n">
-        <v>10.8</v>
+        <v>22.13</v>
       </c>
       <c r="M658" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="659">
@@ -29564,19 +29567,19 @@
         <v>697</v>
       </c>
       <c r="B659" t="n">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C659" t="n">
-        <v>0.537353890178245</v>
+        <v>0.107972772561798</v>
       </c>
       <c r="D659" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E659" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F659" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G659" t="s">
         <v>15</v>
@@ -29585,7 +29588,7 @@
         <v>15</v>
       </c>
       <c r="I659" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="J659" t="s">
         <v>17</v>
@@ -29594,10 +29597,10 @@
         <v>15</v>
       </c>
       <c r="L659" t="n">
-        <v>53.74</v>
+        <v>10.8</v>
       </c>
       <c r="M659" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -29608,13 +29611,13 @@
         <v>816</v>
       </c>
       <c r="C660" t="n">
-        <v>0.795849462390352</v>
+        <v>0.537353890178245</v>
       </c>
       <c r="D660" t="n">
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E660" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F660" t="s">
         <v>26</v>
@@ -29635,10 +29638,10 @@
         <v>15</v>
       </c>
       <c r="L660" t="n">
-        <v>79.58</v>
+        <v>53.74</v>
       </c>
       <c r="M660" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="661">
@@ -29646,10 +29649,10 @@
         <v>699</v>
       </c>
       <c r="B661" t="n">
-        <v>83</v>
+        <v>816</v>
       </c>
       <c r="C661" t="n">
-        <v>0.073919291910315</v>
+        <v>0.795849462390352</v>
       </c>
       <c r="D661" t="n">
         <v>0</v>
@@ -29658,25 +29661,25 @@
         <v>5</v>
       </c>
       <c r="F661" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G661" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H661" t="s">
         <v>15</v>
       </c>
       <c r="I661" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J661" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K661" t="s">
         <v>15</v>
       </c>
       <c r="L661" t="n">
-        <v>7.39</v>
+        <v>79.58</v>
       </c>
       <c r="M661" t="n">
         <v>0</v>
@@ -29690,13 +29693,13 @@
         <v>83</v>
       </c>
       <c r="C662" t="n">
-        <v>0.0625336737736744</v>
+        <v>0.073919291910315</v>
       </c>
       <c r="D662" t="n">
         <v>0</v>
       </c>
       <c r="E662" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F662" t="s">
         <v>104</v>
@@ -29717,7 +29720,7 @@
         <v>15</v>
       </c>
       <c r="L662" t="n">
-        <v>6.25</v>
+        <v>7.39</v>
       </c>
       <c r="M662" t="n">
         <v>0</v>
@@ -29728,16 +29731,16 @@
         <v>701</v>
       </c>
       <c r="B663" t="n">
-        <v>847</v>
+        <v>83</v>
       </c>
       <c r="C663" t="n">
-        <v>0.614087416972055</v>
+        <v>0.0625336737736744</v>
       </c>
       <c r="D663" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="E663" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F663" t="s">
         <v>104</v>
@@ -29758,10 +29761,10 @@
         <v>15</v>
       </c>
       <c r="L663" t="n">
-        <v>61.41</v>
+        <v>6.25</v>
       </c>
       <c r="M663" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="664">
@@ -29772,16 +29775,16 @@
         <v>847</v>
       </c>
       <c r="C664" t="n">
-        <v>0.539831998790722</v>
+        <v>0.614087416972055</v>
       </c>
       <c r="D664" t="n">
-        <v>0.25</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="E664" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F664" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -29799,10 +29802,10 @@
         <v>15</v>
       </c>
       <c r="L664" t="n">
-        <v>53.98</v>
+        <v>61.41</v>
       </c>
       <c r="M664" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="665">
@@ -29810,19 +29813,19 @@
         <v>703</v>
       </c>
       <c r="B665" t="n">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C665" t="n">
-        <v>0.59251665508204</v>
+        <v>0.539831998790722</v>
       </c>
       <c r="D665" t="n">
-        <v>0.225806451612903</v>
+        <v>0.25</v>
       </c>
       <c r="E665" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F665" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G665" t="s">
         <v>20</v>
@@ -29831,7 +29834,7 @@
         <v>15</v>
       </c>
       <c r="I665" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J665" t="s">
         <v>22</v>
@@ -29840,10 +29843,10 @@
         <v>15</v>
       </c>
       <c r="L665" t="n">
-        <v>59.25</v>
+        <v>53.98</v>
       </c>
       <c r="M665" t="n">
-        <v>22.58</v>
+        <v>25</v>
       </c>
     </row>
     <row r="666">
@@ -29854,13 +29857,13 @@
         <v>849</v>
       </c>
       <c r="C666" t="n">
-        <v>0.0843494261280923</v>
+        <v>0.59251665508204</v>
       </c>
       <c r="D666" t="n">
-        <v>0</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="E666" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F666" t="s">
         <v>100</v>
@@ -29881,10 +29884,10 @@
         <v>15</v>
       </c>
       <c r="L666" t="n">
-        <v>8.43</v>
+        <v>59.25</v>
       </c>
       <c r="M666" t="n">
-        <v>0</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="667">
@@ -29895,13 +29898,13 @@
         <v>849</v>
       </c>
       <c r="C667" t="n">
-        <v>0.101291726141322</v>
+        <v>0.0843494261280923</v>
       </c>
       <c r="D667" t="n">
         <v>0</v>
       </c>
       <c r="E667" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F667" t="s">
         <v>100</v>
@@ -29922,7 +29925,7 @@
         <v>15</v>
       </c>
       <c r="L667" t="n">
-        <v>10.13</v>
+        <v>8.43</v>
       </c>
       <c r="M667" t="n">
         <v>0</v>
@@ -29933,19 +29936,19 @@
         <v>706</v>
       </c>
       <c r="B668" t="n">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C668" t="n">
-        <v>0.917033908892498</v>
+        <v>0.101291726141322</v>
       </c>
       <c r="D668" t="n">
-        <v>0.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="E668" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F668" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -29954,19 +29957,19 @@
         <v>15</v>
       </c>
       <c r="I668" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J668" t="s">
         <v>22</v>
       </c>
       <c r="K668" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L668" t="n">
-        <v>91.7</v>
+        <v>10.13</v>
       </c>
       <c r="M668" t="n">
-        <v>57.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -29977,16 +29980,16 @@
         <v>850</v>
       </c>
       <c r="C669" t="n">
-        <v>0.0746483010823231</v>
+        <v>0.917033908892498</v>
       </c>
       <c r="D669" t="n">
-        <v>0.142857142857143</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="E669" t="n">
         <v>6</v>
       </c>
       <c r="F669" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -30001,13 +30004,13 @@
         <v>22</v>
       </c>
       <c r="K669" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L669" t="n">
-        <v>7.46</v>
+        <v>91.7</v>
       </c>
       <c r="M669" t="n">
-        <v>14.29</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="670">
@@ -30015,19 +30018,19 @@
         <v>708</v>
       </c>
       <c r="B670" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C670" t="n">
-        <v>0.115177791032885</v>
+        <v>0.0746483010823231</v>
       </c>
       <c r="D670" t="n">
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E670" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F670" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="G670" t="s">
         <v>20</v>
@@ -30036,7 +30039,7 @@
         <v>15</v>
       </c>
       <c r="I670" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J670" t="s">
         <v>22</v>
@@ -30045,10 +30048,10 @@
         <v>15</v>
       </c>
       <c r="L670" t="n">
-        <v>11.52</v>
+        <v>7.46</v>
       </c>
       <c r="M670" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="671">
@@ -30059,13 +30062,13 @@
         <v>855</v>
       </c>
       <c r="C671" t="n">
-        <v>0.684559343160007</v>
+        <v>0.115177791032885</v>
       </c>
       <c r="D671" t="n">
-        <v>0.189873417721519</v>
+        <v>0</v>
       </c>
       <c r="E671" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F671" t="s">
         <v>33</v>
@@ -30086,10 +30089,10 @@
         <v>15</v>
       </c>
       <c r="L671" t="n">
-        <v>68.46</v>
+        <v>11.52</v>
       </c>
       <c r="M671" t="n">
-        <v>18.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
@@ -30100,13 +30103,13 @@
         <v>855</v>
       </c>
       <c r="C672" t="n">
-        <v>0.655852873990591</v>
+        <v>0.684559343160007</v>
       </c>
       <c r="D672" t="n">
-        <v>0.152173913043478</v>
+        <v>0.189873417721519</v>
       </c>
       <c r="E672" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F672" t="s">
         <v>33</v>
@@ -30127,10 +30130,10 @@
         <v>15</v>
       </c>
       <c r="L672" t="n">
-        <v>65.59</v>
+        <v>68.46</v>
       </c>
       <c r="M672" t="n">
-        <v>15.22</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="673">
@@ -30141,13 +30144,13 @@
         <v>855</v>
       </c>
       <c r="C673" t="n">
-        <v>0.28413962990991</v>
+        <v>0.655852873990591</v>
       </c>
       <c r="D673" t="n">
-        <v>0</v>
+        <v>0.152173913043478</v>
       </c>
       <c r="E673" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F673" t="s">
         <v>33</v>
@@ -30168,10 +30171,10 @@
         <v>15</v>
       </c>
       <c r="L673" t="n">
-        <v>28.41</v>
+        <v>65.59</v>
       </c>
       <c r="M673" t="n">
-        <v>0</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="674">
@@ -30179,19 +30182,19 @@
         <v>712</v>
       </c>
       <c r="B674" t="n">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="C674" t="n">
-        <v>0.408527939650229</v>
+        <v>0.28413962990991</v>
       </c>
       <c r="D674" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E674" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F674" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -30200,7 +30203,7 @@
         <v>15</v>
       </c>
       <c r="I674" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J674" t="s">
         <v>22</v>
@@ -30209,10 +30212,10 @@
         <v>15</v>
       </c>
       <c r="L674" t="n">
-        <v>40.85</v>
+        <v>28.41</v>
       </c>
       <c r="M674" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="675">
@@ -30223,13 +30226,13 @@
         <v>871</v>
       </c>
       <c r="C675" t="n">
-        <v>0.347463209346065</v>
+        <v>0.408527939650229</v>
       </c>
       <c r="D675" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E675" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F675" t="s">
         <v>24</v>
@@ -30250,10 +30253,10 @@
         <v>15</v>
       </c>
       <c r="L675" t="n">
-        <v>34.75</v>
+        <v>40.85</v>
       </c>
       <c r="M675" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="676">
@@ -30264,13 +30267,13 @@
         <v>871</v>
       </c>
       <c r="C676" t="n">
-        <v>0.0883835787043227</v>
+        <v>0.347463209346065</v>
       </c>
       <c r="D676" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E676" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F676" t="s">
         <v>24</v>
@@ -30291,10 +30294,10 @@
         <v>15</v>
       </c>
       <c r="L676" t="n">
-        <v>8.84</v>
+        <v>34.75</v>
       </c>
       <c r="M676" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="677">
@@ -30302,37 +30305,37 @@
         <v>715</v>
       </c>
       <c r="B677" t="n">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C677" t="n">
-        <v>0.189911188826678</v>
+        <v>0.0883835787043227</v>
       </c>
       <c r="D677" t="n">
         <v>0</v>
       </c>
       <c r="E677" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F677" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G677" t="s">
         <v>20</v>
       </c>
       <c r="H677" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I677" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J677" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K677" t="s">
         <v>15</v>
       </c>
       <c r="L677" t="n">
-        <v>18.99</v>
+        <v>8.84</v>
       </c>
       <c r="M677" t="n">
         <v>0</v>
@@ -30346,13 +30349,13 @@
         <v>877</v>
       </c>
       <c r="C678" t="n">
-        <v>0.238384263224329</v>
+        <v>0.189911188826678</v>
       </c>
       <c r="D678" t="n">
-        <v>0.0683760683760684</v>
+        <v>0</v>
       </c>
       <c r="E678" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F678" t="s">
         <v>33</v>
@@ -30373,10 +30376,10 @@
         <v>15</v>
       </c>
       <c r="L678" t="n">
-        <v>23.84</v>
+        <v>18.99</v>
       </c>
       <c r="M678" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
@@ -30384,40 +30387,40 @@
         <v>717</v>
       </c>
       <c r="B679" t="n">
-        <v>908</v>
+        <v>877</v>
       </c>
       <c r="C679" t="n">
-        <v>0.985297830500998</v>
+        <v>0.238384263224329</v>
       </c>
       <c r="D679" t="n">
-        <v>0.538461538461538</v>
+        <v>0.0683760683760684</v>
       </c>
       <c r="E679" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F679" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="G679" t="s">
         <v>20</v>
       </c>
       <c r="H679" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I679" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J679" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K679" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L679" t="n">
-        <v>98.53</v>
+        <v>23.84</v>
       </c>
       <c r="M679" t="n">
-        <v>53.85</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="680">
@@ -30425,19 +30428,19 @@
         <v>718</v>
       </c>
       <c r="B680" t="n">
-        <v>91</v>
+        <v>908</v>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>0.985297830500998</v>
       </c>
       <c r="D680" t="n">
-        <v>0.803846153846154</v>
+        <v>0.538461538461538</v>
       </c>
       <c r="E680" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F680" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G680" t="s">
         <v>20</v>
@@ -30449,16 +30452,16 @@
         <v>21</v>
       </c>
       <c r="J680" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K680" t="s">
         <v>20</v>
       </c>
       <c r="L680" t="n">
-        <v>100</v>
+        <v>98.53</v>
       </c>
       <c r="M680" t="n">
-        <v>80.38</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="681">
@@ -30472,10 +30475,10 @@
         <v>1</v>
       </c>
       <c r="D681" t="n">
-        <v>0.752491694352159</v>
+        <v>0.803846153846154</v>
       </c>
       <c r="E681" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F681" t="s">
         <v>26</v>
@@ -30499,7 +30502,7 @@
         <v>100</v>
       </c>
       <c r="M681" t="n">
-        <v>75.25</v>
+        <v>80.38</v>
       </c>
     </row>
     <row r="682">
@@ -30513,10 +30516,10 @@
         <v>1</v>
       </c>
       <c r="D682" t="n">
-        <v>0.983455882352941</v>
+        <v>0.752491694352159</v>
       </c>
       <c r="E682" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F682" t="s">
         <v>26</v>
@@ -30540,7 +30543,7 @@
         <v>100</v>
       </c>
       <c r="M682" t="n">
-        <v>98.35</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="683">
@@ -30554,10 +30557,10 @@
         <v>1</v>
       </c>
       <c r="D683" t="n">
-        <v>0.870967741935484</v>
+        <v>0.983455882352941</v>
       </c>
       <c r="E683" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="F683" t="s">
         <v>26</v>
@@ -30581,7 +30584,7 @@
         <v>100</v>
       </c>
       <c r="M683" t="n">
-        <v>87.1</v>
+        <v>98.35</v>
       </c>
     </row>
     <row r="684">
@@ -30595,10 +30598,10 @@
         <v>1</v>
       </c>
       <c r="D684" t="n">
-        <v>0.916666666666667</v>
+        <v>0.870967741935484</v>
       </c>
       <c r="E684" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F684" t="s">
         <v>26</v>
@@ -30622,7 +30625,7 @@
         <v>100</v>
       </c>
       <c r="M684" t="n">
-        <v>91.67</v>
+        <v>87.1</v>
       </c>
     </row>
     <row r="685">
@@ -30636,10 +30639,10 @@
         <v>1</v>
       </c>
       <c r="D685" t="n">
-        <v>0.923664122137405</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="E685" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F685" t="s">
         <v>26</v>
@@ -30663,7 +30666,7 @@
         <v>100</v>
       </c>
       <c r="M685" t="n">
-        <v>92.37</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="686">
@@ -30677,10 +30680,10 @@
         <v>1</v>
       </c>
       <c r="D686" t="n">
-        <v>0.934210526315789</v>
+        <v>0.923664122137405</v>
       </c>
       <c r="E686" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F686" t="s">
         <v>26</v>
@@ -30704,7 +30707,7 @@
         <v>100</v>
       </c>
       <c r="M686" t="n">
-        <v>93.42</v>
+        <v>92.37</v>
       </c>
     </row>
     <row r="687">
@@ -30718,10 +30721,10 @@
         <v>1</v>
       </c>
       <c r="D687" t="n">
-        <v>0.822222222222222</v>
+        <v>0.934210526315789</v>
       </c>
       <c r="E687" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F687" t="s">
         <v>26</v>
@@ -30745,7 +30748,7 @@
         <v>100</v>
       </c>
       <c r="M687" t="n">
-        <v>82.22</v>
+        <v>93.42</v>
       </c>
     </row>
     <row r="688">
@@ -30759,10 +30762,10 @@
         <v>1</v>
       </c>
       <c r="D688" t="n">
-        <v>0.947136563876652</v>
+        <v>0.822222222222222</v>
       </c>
       <c r="E688" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="F688" t="s">
         <v>26</v>
@@ -30786,7 +30789,7 @@
         <v>100</v>
       </c>
       <c r="M688" t="n">
-        <v>94.71</v>
+        <v>82.22</v>
       </c>
     </row>
     <row r="689">
@@ -30800,10 +30803,10 @@
         <v>1</v>
       </c>
       <c r="D689" t="n">
-        <v>1</v>
+        <v>0.947136563876652</v>
       </c>
       <c r="E689" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="F689" t="s">
         <v>26</v>
@@ -30827,7 +30830,7 @@
         <v>100</v>
       </c>
       <c r="M689" t="n">
-        <v>100</v>
+        <v>94.71</v>
       </c>
     </row>
     <row r="690">
@@ -30841,10 +30844,10 @@
         <v>1</v>
       </c>
       <c r="D690" t="n">
-        <v>0.790697674418605</v>
+        <v>1</v>
       </c>
       <c r="E690" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F690" t="s">
         <v>26</v>
@@ -30868,7 +30871,7 @@
         <v>100</v>
       </c>
       <c r="M690" t="n">
-        <v>79.07</v>
+        <v>100</v>
       </c>
     </row>
     <row r="691">
@@ -30882,10 +30885,10 @@
         <v>1</v>
       </c>
       <c r="D691" t="n">
-        <v>1</v>
+        <v>0.790697674418605</v>
       </c>
       <c r="E691" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F691" t="s">
         <v>26</v>
@@ -30909,7 +30912,7 @@
         <v>100</v>
       </c>
       <c r="M691" t="n">
-        <v>100</v>
+        <v>79.07</v>
       </c>
     </row>
     <row r="692">
@@ -30917,19 +30920,19 @@
         <v>730</v>
       </c>
       <c r="B692" t="n">
-        <v>912</v>
+        <v>91</v>
       </c>
       <c r="C692" t="n">
-        <v>0.836839411302712</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E692" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F692" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -30938,19 +30941,19 @@
         <v>15</v>
       </c>
       <c r="I692" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J692" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K692" t="s">
         <v>20</v>
       </c>
       <c r="L692" t="n">
-        <v>83.68</v>
+        <v>100</v>
       </c>
       <c r="M692" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="693">
@@ -30961,13 +30964,13 @@
         <v>912</v>
       </c>
       <c r="C693" t="n">
-        <v>0.999275760557554</v>
+        <v>0.836839411302712</v>
       </c>
       <c r="D693" t="n">
-        <v>0.801980198019802</v>
+        <v>0.6</v>
       </c>
       <c r="E693" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F693" t="s">
         <v>129</v>
@@ -30988,10 +30991,10 @@
         <v>20</v>
       </c>
       <c r="L693" t="n">
-        <v>99.93</v>
+        <v>83.68</v>
       </c>
       <c r="M693" t="n">
-        <v>80.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="694">
@@ -30999,19 +31002,19 @@
         <v>732</v>
       </c>
       <c r="B694" t="n">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="C694" t="n">
-        <v>0.256192576362544</v>
+        <v>0.999275760557554</v>
       </c>
       <c r="D694" t="n">
-        <v>0.234375</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="E694" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F694" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -31020,19 +31023,19 @@
         <v>15</v>
       </c>
       <c r="I694" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J694" t="s">
         <v>22</v>
       </c>
       <c r="K694" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L694" t="n">
-        <v>25.62</v>
+        <v>99.93</v>
       </c>
       <c r="M694" t="n">
-        <v>23.44</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="695">
@@ -31043,13 +31046,13 @@
         <v>936</v>
       </c>
       <c r="C695" t="n">
-        <v>0.126528885603394</v>
+        <v>0.256192576362544</v>
       </c>
       <c r="D695" t="n">
-        <v>0.244897959183673</v>
+        <v>0.234375</v>
       </c>
       <c r="E695" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F695" t="s">
         <v>90</v>
@@ -31070,10 +31073,10 @@
         <v>15</v>
       </c>
       <c r="L695" t="n">
-        <v>12.65</v>
+        <v>25.62</v>
       </c>
       <c r="M695" t="n">
-        <v>24.49</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="696">
@@ -31084,16 +31087,16 @@
         <v>936</v>
       </c>
       <c r="C696" t="n">
-        <v>0.145772823192471</v>
+        <v>0.126528885603394</v>
       </c>
       <c r="D696" t="n">
-        <v>0</v>
+        <v>0.244897959183673</v>
       </c>
       <c r="E696" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F696" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G696" t="s">
         <v>20</v>
@@ -31111,10 +31114,10 @@
         <v>15</v>
       </c>
       <c r="L696" t="n">
-        <v>14.58</v>
+        <v>12.65</v>
       </c>
       <c r="M696" t="n">
-        <v>0</v>
+        <v>24.49</v>
       </c>
     </row>
     <row r="697">
@@ -31122,19 +31125,19 @@
         <v>735</v>
       </c>
       <c r="B697" t="n">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C697" t="n">
-        <v>0.459095571837978</v>
+        <v>0.145772823192471</v>
       </c>
       <c r="D697" t="n">
-        <v>0.26865671641791</v>
+        <v>0</v>
       </c>
       <c r="E697" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F697" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="G697" t="s">
         <v>20</v>
@@ -31143,7 +31146,7 @@
         <v>15</v>
       </c>
       <c r="I697" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J697" t="s">
         <v>22</v>
@@ -31152,10 +31155,10 @@
         <v>15</v>
       </c>
       <c r="L697" t="n">
-        <v>45.91</v>
+        <v>14.58</v>
       </c>
       <c r="M697" t="n">
-        <v>26.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="698">
@@ -31166,13 +31169,13 @@
         <v>939</v>
       </c>
       <c r="C698" t="n">
-        <v>0.273805860039174</v>
+        <v>0.459095571837978</v>
       </c>
       <c r="D698" t="n">
-        <v>0.113207547169811</v>
+        <v>0.26865671641791</v>
       </c>
       <c r="E698" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F698" t="s">
         <v>14</v>
@@ -31193,10 +31196,10 @@
         <v>15</v>
       </c>
       <c r="L698" t="n">
-        <v>27.38</v>
+        <v>45.91</v>
       </c>
       <c r="M698" t="n">
-        <v>11.32</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="699">
@@ -31204,19 +31207,19 @@
         <v>737</v>
       </c>
       <c r="B699" t="n">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C699" t="n">
-        <v>0.530260127089699</v>
+        <v>0.273805860039174</v>
       </c>
       <c r="D699" t="n">
-        <v>0.307692307692308</v>
+        <v>0.113207547169811</v>
       </c>
       <c r="E699" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F699" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -31225,7 +31228,7 @@
         <v>15</v>
       </c>
       <c r="I699" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J699" t="s">
         <v>22</v>
@@ -31234,10 +31237,10 @@
         <v>15</v>
       </c>
       <c r="L699" t="n">
-        <v>53.03</v>
+        <v>27.38</v>
       </c>
       <c r="M699" t="n">
-        <v>30.77</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="700">
@@ -31248,13 +31251,13 @@
         <v>952</v>
       </c>
       <c r="C700" t="n">
-        <v>0.279081110924314</v>
+        <v>0.530260127089699</v>
       </c>
       <c r="D700" t="n">
-        <v>0.1875</v>
+        <v>0.307692307692308</v>
       </c>
       <c r="E700" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F700" t="s">
         <v>100</v>
@@ -31275,10 +31278,10 @@
         <v>15</v>
       </c>
       <c r="L700" t="n">
-        <v>27.91</v>
+        <v>53.03</v>
       </c>
       <c r="M700" t="n">
-        <v>18.75</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="701">
@@ -31289,13 +31292,13 @@
         <v>952</v>
       </c>
       <c r="C701" t="n">
-        <v>0.459170669401345</v>
+        <v>0.279081110924314</v>
       </c>
       <c r="D701" t="n">
-        <v>0.333333333333333</v>
+        <v>0.1875</v>
       </c>
       <c r="E701" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F701" t="s">
         <v>100</v>
@@ -31316,10 +31319,10 @@
         <v>15</v>
       </c>
       <c r="L701" t="n">
-        <v>45.92</v>
+        <v>27.91</v>
       </c>
       <c r="M701" t="n">
-        <v>33.33</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="702">
@@ -31327,19 +31330,19 @@
         <v>740</v>
       </c>
       <c r="B702" t="n">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="C702" t="n">
-        <v>0.236552407190299</v>
+        <v>0.459170669401345</v>
       </c>
       <c r="D702" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E702" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F702" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G702" t="s">
         <v>20</v>
@@ -31348,7 +31351,7 @@
         <v>15</v>
       </c>
       <c r="I702" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J702" t="s">
         <v>22</v>
@@ -31357,10 +31360,10 @@
         <v>15</v>
       </c>
       <c r="L702" t="n">
-        <v>23.66</v>
+        <v>45.92</v>
       </c>
       <c r="M702" t="n">
-        <v>12.5</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="703">
@@ -31368,19 +31371,19 @@
         <v>741</v>
       </c>
       <c r="B703" t="n">
-        <v>996</v>
+        <v>963</v>
       </c>
       <c r="C703" t="n">
-        <v>0.607923940151804</v>
+        <v>0.236552407190299</v>
       </c>
       <c r="D703" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="E703" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F703" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G703" t="s">
         <v>20</v>
@@ -31389,19 +31392,19 @@
         <v>15</v>
       </c>
       <c r="I703" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J703" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K703" t="s">
         <v>15</v>
       </c>
       <c r="L703" t="n">
-        <v>60.79</v>
+        <v>23.66</v>
       </c>
       <c r="M703" t="n">
-        <v>33.33</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="704">
@@ -31412,13 +31415,13 @@
         <v>996</v>
       </c>
       <c r="C704" t="n">
-        <v>0.49126309524667</v>
+        <v>0.607923940151804</v>
       </c>
       <c r="D704" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E704" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F704" t="s">
         <v>14</v>
@@ -31439,10 +31442,10 @@
         <v>15</v>
       </c>
       <c r="L704" t="n">
-        <v>49.13</v>
+        <v>60.79</v>
       </c>
       <c r="M704" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="705">
@@ -31453,13 +31456,13 @@
         <v>996</v>
       </c>
       <c r="C705" t="n">
-        <v>0.914669142135063</v>
+        <v>0.49126309524667</v>
       </c>
       <c r="D705" t="n">
-        <v>0.666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="E705" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F705" t="s">
         <v>14</v>
@@ -31477,13 +31480,13 @@
         <v>17</v>
       </c>
       <c r="K705" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L705" t="n">
-        <v>91.47</v>
+        <v>49.13</v>
       </c>
       <c r="M705" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="706">
@@ -31494,13 +31497,13 @@
         <v>996</v>
       </c>
       <c r="C706" t="n">
-        <v>0.942872064009285</v>
+        <v>0.914669142135063</v>
       </c>
       <c r="D706" t="n">
-        <v>0.8</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="E706" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F706" t="s">
         <v>14</v>
@@ -31521,10 +31524,10 @@
         <v>20</v>
       </c>
       <c r="L706" t="n">
-        <v>94.29</v>
+        <v>91.47</v>
       </c>
       <c r="M706" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="707">
@@ -31535,13 +31538,13 @@
         <v>996</v>
       </c>
       <c r="C707" t="n">
-        <v>0.994057899429126</v>
+        <v>0.942872064009285</v>
       </c>
       <c r="D707" t="n">
-        <v>0.833333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="E707" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F707" t="s">
         <v>14</v>
@@ -31562,10 +31565,10 @@
         <v>20</v>
       </c>
       <c r="L707" t="n">
-        <v>99.41</v>
+        <v>94.29</v>
       </c>
       <c r="M707" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="708">
@@ -31576,10 +31579,10 @@
         <v>996</v>
       </c>
       <c r="C708" t="n">
-        <v>0.945974716497023</v>
+        <v>0.994057899429126</v>
       </c>
       <c r="D708" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E708" t="n">
         <v>6</v>
@@ -31603,9 +31606,50 @@
         <v>20</v>
       </c>
       <c r="L708" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="M708" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s">
+        <v>747</v>
+      </c>
+      <c r="B709" t="n">
+        <v>996</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.945974716497023</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E709" t="n">
+        <v>6</v>
+      </c>
+      <c r="F709" t="s">
+        <v>14</v>
+      </c>
+      <c r="G709" t="s">
+        <v>20</v>
+      </c>
+      <c r="H709" t="s">
+        <v>15</v>
+      </c>
+      <c r="I709" t="s">
+        <v>21</v>
+      </c>
+      <c r="J709" t="s">
+        <v>17</v>
+      </c>
+      <c r="K709" t="s">
+        <v>20</v>
+      </c>
+      <c r="L709" t="n">
         <v>94.6</v>
       </c>
-      <c r="M708" t="n">
+      <c r="M709" t="n">
         <v>66.67</v>
       </c>
     </row>
